--- a/NSF Standard 2025/COA/coa-v1.xlsx
+++ b/NSF Standard 2025/COA/coa-v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10905"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8612F87E-4F01-0843-9E40-4D518093DB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50071C85-F6C0-1A46-84C0-FB455586ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="17920" windowHeight="20320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NSF COA Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" iterateCount="1" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="150">
   <si>
     <t>G:</t>
   </si>
@@ -480,9 +480,6 @@
     <t>Sayrafi, Mahrud</t>
   </si>
   <si>
-    <t>Yang, Jay</t>
-  </si>
-  <si>
     <t>Chan, Melody</t>
   </si>
   <si>
@@ -492,48 +489,12 @@
     <t>Corey, Daniel</t>
   </si>
   <si>
-    <t>Goldstein, Steve</t>
-  </si>
-  <si>
-    <t>sgoldstein@wisc.edu</t>
-  </si>
-  <si>
-    <t>Laudone, Robert, P</t>
-  </si>
-  <si>
-    <t>Robert.laudone@gmail.com</t>
-  </si>
-  <si>
-    <t>Almousa, Ayah</t>
-  </si>
-  <si>
     <t>University of Minnesota - Twin Cities</t>
   </si>
   <si>
-    <t>Loper, Michael, C</t>
-  </si>
-  <si>
-    <t>University of Wisconsin - River Falls</t>
-  </si>
-  <si>
-    <t>michael.loper@uwrf.edu</t>
-  </si>
-  <si>
-    <t>University of Wisconsin - Madison</t>
-  </si>
-  <si>
     <t>University of California - Berkeley</t>
   </si>
   <si>
-    <t>Li, Wanlin</t>
-  </si>
-  <si>
-    <t>Washington University in St. Louis</t>
-  </si>
-  <si>
-    <t>wanlin@wustl.edu</t>
-  </si>
-  <si>
     <t>melody_chan@brown.edu</t>
   </si>
   <si>
@@ -555,9 +516,6 @@
     <t>gwynm@math.harvard.edu</t>
   </si>
   <si>
-    <t>Wolfe, Corey</t>
-  </si>
-  <si>
     <t>University of Tulane</t>
   </si>
   <si>
@@ -567,12 +525,6 @@
     <t>Ramkumar, Ritvik</t>
   </si>
   <si>
-    <t>ritvikr@cornell.edu</t>
-  </si>
-  <si>
-    <t>Cornell University</t>
-  </si>
-  <si>
     <t>Eisenbud, David</t>
   </si>
   <si>
@@ -645,15 +597,6 @@
     <t>knewton@dvc.edu</t>
   </si>
   <si>
-    <t>Chapman, Scott</t>
-  </si>
-  <si>
-    <t>Sam Houston State University</t>
-  </si>
-  <si>
-    <t>Communications in Algebra</t>
-  </si>
-  <si>
     <t>Hering, Milena</t>
   </si>
   <si>
@@ -699,15 +642,6 @@
     <t>University of Nevada - Las Vegas</t>
   </si>
   <si>
-    <t>Max Plank Institute, Mathematics in the Sciences</t>
-  </si>
-  <si>
-    <t>mahrud@mis.mpg.de</t>
-  </si>
-  <si>
-    <t>United States Naval Academy</t>
-  </si>
-  <si>
     <t>Vanderbilt Universtiy</t>
   </si>
   <si>
@@ -717,24 +651,12 @@
     <t>Assaf, Eran</t>
   </si>
   <si>
-    <t>eran.assaf@dartmouth.edu</t>
-  </si>
-  <si>
     <t>Vlad, Raluca</t>
   </si>
   <si>
     <t>raluca_vlad@brown.edu</t>
   </si>
   <si>
-    <t>jayy@wustl.edu</t>
-  </si>
-  <si>
-    <t>University of South Carolina</t>
-  </si>
-  <si>
-    <t>aalmousa@sc.edu</t>
-  </si>
-  <si>
     <t>Huang, Daoji</t>
   </si>
   <si>
@@ -760,6 +682,90 @@
   </si>
   <si>
     <t>serkan@sfsu.edu</t>
+  </si>
+  <si>
+    <t>DeGroot, William</t>
+  </si>
+  <si>
+    <t>william.h.degroot.gr@dartmouth.edu</t>
+  </si>
+  <si>
+    <t>Banks, Maya</t>
+  </si>
+  <si>
+    <t>University of Illinois, Chicago</t>
+  </si>
+  <si>
+    <t>mayadb@uic.edu</t>
+  </si>
+  <si>
+    <t>Massachusetts Institute of Technology</t>
+  </si>
+  <si>
+    <t>eranasaf@mit.edu</t>
+  </si>
+  <si>
+    <t>Bucciarelli, Jacob</t>
+  </si>
+  <si>
+    <t>Kansas State University</t>
+  </si>
+  <si>
+    <t>jbucciarelli@ksu.edu</t>
+  </si>
+  <si>
+    <t>Cobb, John</t>
+  </si>
+  <si>
+    <t>Auburn University</t>
+  </si>
+  <si>
+    <t>jdcobb3@gmail.com</t>
+  </si>
+  <si>
+    <t>Manon, Christopher</t>
+  </si>
+  <si>
+    <t>University of Kentucky</t>
+  </si>
+  <si>
+    <t>christopher.manon@uky.edu</t>
+  </si>
+  <si>
+    <t>University of Notre Dame</t>
+  </si>
+  <si>
+    <t>rramkuma@nd.edu</t>
+  </si>
+  <si>
+    <t>McMaster University</t>
+  </si>
+  <si>
+    <t>mahrud@mcmaster.ca</t>
+  </si>
+  <si>
+    <t>Seceleanu, Alexandra</t>
+  </si>
+  <si>
+    <t>aseceleanu@unl.edu</t>
+  </si>
+  <si>
+    <t>Huybrechts, Daniel</t>
+  </si>
+  <si>
+    <t>Universität Bonn</t>
+  </si>
+  <si>
+    <t>Journal für die reine und angewandte Mathematik</t>
+  </si>
+  <si>
+    <t>Payne, Sam</t>
+  </si>
+  <si>
+    <t>University of Michigan</t>
+  </si>
+  <si>
+    <t>Selecta Mathematica</t>
   </si>
 </sst>
 </file>
@@ -1103,10 +1109,6 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -1235,6 +1237,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2657,223 +2663,219 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="88" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="1:5" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
     </row>
     <row r="4" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
     </row>
     <row r="5" spans="1:5" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
     </row>
     <row r="7" spans="1:5" s="6" customFormat="1" ht="124" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
     </row>
     <row r="9" spans="1:5" ht="38.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
     </row>
     <row r="10" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
     </row>
     <row r="11" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
     </row>
     <row r="12" spans="1:5" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" spans="1:5" ht="49.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
     </row>
     <row r="14" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
     </row>
     <row r="15" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="48" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="30"/>
+      <c r="C17" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="29"/>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="32">
-        <v>45473</v>
-      </c>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" s="7" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="54"/>
-      <c r="B24" s="42" t="s">
+      <c r="A24" s="53"/>
+      <c r="B24" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
@@ -2885,19 +2887,19 @@
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="51" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2911,8 +2913,8 @@
       <c r="C28" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="57" t="s">
-        <v>108</v>
+      <c r="D28" s="56" t="s">
+        <v>92</v>
       </c>
       <c r="E28" s="12"/>
     </row>
@@ -2924,25 +2926,25 @@
       <c r="E29" s="12"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="28"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="27"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="28"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="28"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
@@ -2952,13 +2954,13 @@
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="68.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
     </row>
     <row r="35" spans="1:5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -2968,16 +2970,16 @@
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D37" s="52" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2989,49 +2991,55 @@
         <v>49</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" s="56" t="s">
-        <v>122</v>
+        <v>102</v>
+      </c>
+      <c r="D38" s="55" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="24"/>
+      <c r="B39" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="22"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="22"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="27"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="26"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="10"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="27"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="26"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="27"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
     </row>
     <row r="45" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
@@ -3041,38 +3049,38 @@
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
     </row>
     <row r="47" spans="1:5" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="45" t="s">
+      <c r="A47" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48" s="45" t="s">
+      <c r="A48" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="46"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="45"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="45"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="46"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="45"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
@@ -3084,83 +3092,85 @@
       <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B51" s="51" t="s">
+      <c r="B51" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="51" t="s">
+      <c r="D51" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="52" t="s">
+      <c r="E51" s="51" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>137</v>
+        <v>3</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="D52" s="57" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="E52" s="12">
-        <v>43970</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>91</v>
+      <c r="B53" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>127</v>
       </c>
       <c r="D53" s="58" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E53" s="12"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="C54" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D54" s="59" t="s">
-        <v>133</v>
+        <v>3</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="58" t="s">
+        <v>126</v>
       </c>
       <c r="E54" s="12"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D55" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="E55" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="12">
+        <v>45444</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
@@ -3170,42 +3180,46 @@
         <v>50</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="56" t="s">
         <v>51</v>
       </c>
       <c r="E56" s="12"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="13" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D57" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="E57" s="12"/>
+        <v>87</v>
+      </c>
+      <c r="D57" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="12">
+        <v>45292</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D58" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E58" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="D58" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" s="12">
+        <v>45444</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="13" t="s">
@@ -3215,10 +3229,10 @@
         <v>52</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D59" s="57" t="s">
-        <v>131</v>
+        <v>108</v>
+      </c>
+      <c r="D59" s="56" t="s">
+        <v>109</v>
       </c>
       <c r="E59" s="12"/>
     </row>
@@ -3227,13 +3241,13 @@
         <v>3</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D60" s="57" t="s">
-        <v>106</v>
+        <v>130</v>
+      </c>
+      <c r="D60" s="56" t="s">
+        <v>131</v>
       </c>
       <c r="E60" s="12"/>
     </row>
@@ -3242,16 +3256,16 @@
         <v>3</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D61" s="57" t="s">
-        <v>97</v>
+        <v>89</v>
+      </c>
+      <c r="D61" s="56" t="s">
+        <v>90</v>
       </c>
       <c r="E61" s="12">
-        <v>44774</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -3259,13 +3273,13 @@
         <v>7</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D62" s="57" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="D62" s="56" t="s">
+        <v>81</v>
       </c>
       <c r="E62" s="12"/>
     </row>
@@ -3274,13 +3288,13 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="57" t="s">
-        <v>125</v>
+        <v>47</v>
+      </c>
+      <c r="D63" s="56" t="s">
+        <v>59</v>
       </c>
       <c r="E63" s="12"/>
     </row>
@@ -3289,13 +3303,13 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D64" s="57" t="s">
-        <v>124</v>
+        <v>133</v>
+      </c>
+      <c r="D64" s="56" t="s">
+        <v>134</v>
       </c>
       <c r="E64" s="12"/>
     </row>
@@ -3304,30 +3318,28 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D65" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" s="12">
-        <v>44773</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="D65" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="E65" s="12"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>122</v>
+        <v>104</v>
+      </c>
+      <c r="D66" s="56" t="s">
+        <v>105</v>
       </c>
       <c r="E66" s="12"/>
     </row>
@@ -3336,16 +3348,16 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>59</v>
+      <c r="D67" s="56" t="s">
+        <v>70</v>
       </c>
       <c r="E67" s="12">
-        <v>44315</v>
+        <v>44773</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -3353,13 +3365,13 @@
         <v>3</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E68" s="12"/>
     </row>
@@ -3368,13 +3380,13 @@
         <v>3</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E69" s="12"/>
     </row>
@@ -3383,63 +3395,65 @@
         <v>3</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E70" s="12"/>
+        <v>121</v>
+      </c>
+      <c r="E70" s="12">
+        <v>45444</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E71" s="12">
-        <v>44774</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E71" s="12"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E72" s="12"/>
+        <v>83</v>
+      </c>
+      <c r="E72" s="12">
+        <v>44774</v>
+      </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E73" s="12">
-        <v>44315</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -3447,47 +3461,43 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E74" s="12">
-        <v>43652</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E74" s="12"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E75" s="12">
-        <v>43970</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="E75" s="12"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E76" s="12"/>
     </row>
@@ -3496,13 +3506,13 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E77" s="12">
         <v>44743</v>
@@ -3513,13 +3523,13 @@
         <v>7</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E78" s="12">
         <v>44743</v>
@@ -3530,28 +3540,30 @@
         <v>3</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E79" s="12"/>
+        <v>139</v>
+      </c>
+      <c r="E79" s="12">
+        <v>44773</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E80" s="12"/>
     </row>
@@ -3563,77 +3575,75 @@
         <v>53</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E81" s="20"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="13" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E82" s="18">
-        <v>44743</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E82" s="18"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B83" s="29" t="s">
-        <v>134</v>
+      <c r="B83" s="16" t="s">
+        <v>53</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D83" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" s="22"/>
+        <v>66</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E83" s="18">
+        <v>44743</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D84" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E84" s="21"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B84" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C84" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D84" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E84" s="18">
+      <c r="B85" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E85" s="18">
         <v>44774</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C85" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D85" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" s="22">
-        <v>44315</v>
       </c>
     </row>
     <row r="86" spans="1:5" s="2" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3644,38 +3654,38 @@
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5" s="2" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="41" t="s">
+      <c r="A87" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B87" s="41"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
     </row>
     <row r="88" spans="1:5" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A88" s="42" t="s">
+      <c r="A88" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B88" s="42"/>
-      <c r="C88" s="42"/>
-      <c r="D88" s="42"/>
-      <c r="E88" s="43"/>
+      <c r="B88" s="41"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="42"/>
     </row>
     <row r="89" spans="1:5" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A89" s="42" t="s">
+      <c r="A89" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B89" s="42"/>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
-      <c r="E89" s="43"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="42"/>
     </row>
     <row r="90" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="42"/>
-      <c r="B90" s="42"/>
-      <c r="C90" s="42"/>
-      <c r="D90" s="42"/>
-      <c r="E90" s="43"/>
+      <c r="A90" s="41"/>
+      <c r="B90" s="41"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="41"/>
+      <c r="E90" s="42"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
@@ -3687,19 +3697,19 @@
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="50" t="s">
+      <c r="A92" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="B92" s="51" t="s">
+      <c r="B92" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C92" s="51" t="s">
+      <c r="C92" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D92" s="51" t="s">
+      <c r="D92" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E92" s="52" t="s">
+      <c r="E92" s="51" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3708,24 +3718,32 @@
         <v>9</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E93" s="18">
-        <v>44713</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="D93" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="E93" s="18"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="10"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="12"/>
+      <c r="A94" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E94" s="12">
+        <v>45839</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="13"/>
@@ -3776,46 +3794,40 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D81" r:id="rId1" xr:uid="{904767E0-458D-1347-8BB9-1976BB1FF1D1}"/>
-    <hyperlink ref="D73" r:id="rId2" xr:uid="{D663B8B8-7E57-8649-9DD2-B5D497264390}"/>
-    <hyperlink ref="D52" r:id="rId3" xr:uid="{398A43CE-C18A-0B44-B856-F0801B930E24}"/>
-    <hyperlink ref="D75" r:id="rId4" xr:uid="{8C29DDB8-8B49-4347-A3C3-CE43F0797091}"/>
-    <hyperlink ref="D74" r:id="rId5" xr:uid="{71DE6A9B-BFA9-1E4C-B8F2-6A3C04709908}"/>
-    <hyperlink ref="D59" r:id="rId6" xr:uid="{6F054ADE-2128-A242-A68C-A98A435575F1}"/>
-    <hyperlink ref="D62" r:id="rId7" xr:uid="{104A15BE-6247-3246-BEE5-EA30848B3F2A}"/>
-    <hyperlink ref="D77" r:id="rId8" xr:uid="{827ECAD7-5213-354D-A361-5FAB9B0E475C}"/>
-    <hyperlink ref="D78" r:id="rId9" xr:uid="{CAF9D624-66F8-6445-B341-5FB7814EA1EC}"/>
-    <hyperlink ref="D82" r:id="rId10" xr:uid="{638D7115-B753-7841-8C7D-0B0E8620F45D}"/>
-    <hyperlink ref="D79" r:id="rId11" xr:uid="{8E4D040C-F2AD-264E-BFBB-EC5BA1EB8EA6}"/>
-    <hyperlink ref="D65" r:id="rId12" xr:uid="{B0A10FCD-E7C8-7441-90E2-775A95245FD0}"/>
-    <hyperlink ref="D72" r:id="rId13" xr:uid="{DA634E74-5A9A-A74A-A057-2850D4DCA3C0}"/>
-    <hyperlink ref="D61" r:id="rId14" xr:uid="{AC3ABC1A-9AA0-CE46-A47E-B3234A5FF6B2}"/>
-    <hyperlink ref="D71" r:id="rId15" xr:uid="{3B163028-53CA-494B-82BE-90E411436806}"/>
-    <hyperlink ref="D80" r:id="rId16" xr:uid="{685592B0-9268-3D48-8F20-5C3CACABCFD0}"/>
-    <hyperlink ref="D56" r:id="rId17" xr:uid="{8BD21104-6AFB-C946-AA90-6012C50A26B8}"/>
-    <hyperlink ref="D60" r:id="rId18" xr:uid="{66D220BB-3E9C-C64A-AA62-57D3833607E9}"/>
-    <hyperlink ref="D57" r:id="rId19" xr:uid="{2C7A6E24-40B5-2346-9892-F12ACF4DDF91}"/>
-    <hyperlink ref="D28" r:id="rId20" xr:uid="{C3C366B6-6021-0245-BEDE-4316A28D84CC}"/>
-    <hyperlink ref="D68" r:id="rId21" xr:uid="{862F3999-5590-7148-96F2-8F15222D0607}"/>
-    <hyperlink ref="D76" r:id="rId22" xr:uid="{B8AF1858-6D7F-DF4D-B017-602EA3A527DC}"/>
-    <hyperlink ref="D38" r:id="rId23" xr:uid="{FA050B20-899B-0346-BF0B-7A0573B5A76E}"/>
-    <hyperlink ref="D63" r:id="rId24" xr:uid="{ACB0011A-58C2-8F49-9668-853012316F50}"/>
-    <hyperlink ref="D66" r:id="rId25" xr:uid="{0417B0F2-2C76-E543-A1C1-3CA198E8BBC1}"/>
-    <hyperlink ref="D54" r:id="rId26" xr:uid="{499B0A61-0766-B841-B52B-BF74EA90DAE9}"/>
-    <hyperlink ref="D85" r:id="rId27" xr:uid="{650573DA-892B-6A4E-90EC-94589536B559}"/>
-    <hyperlink ref="D83" r:id="rId28" xr:uid="{789528BE-1991-3848-8F01-726B0F3930FF}"/>
-    <hyperlink ref="D70" r:id="rId29" xr:uid="{4B905BA4-2AE4-BB44-A4C8-BF91D2154158}"/>
-    <hyperlink ref="D53" r:id="rId30" xr:uid="{BA5F5B35-C6BA-F140-9FBC-2E8E17C7E43B}"/>
-    <hyperlink ref="D55" r:id="rId31" xr:uid="{9ED1B634-F68E-AA42-8024-AE9A0D9B46E1}"/>
-    <hyperlink ref="D69" r:id="rId32" xr:uid="{D6F911B6-BCA0-D447-B151-E3ABC512AA7A}"/>
+    <hyperlink ref="D59" r:id="rId2" xr:uid="{6F054ADE-2128-A242-A68C-A98A435575F1}"/>
+    <hyperlink ref="D77" r:id="rId3" xr:uid="{827ECAD7-5213-354D-A361-5FAB9B0E475C}"/>
+    <hyperlink ref="D78" r:id="rId4" xr:uid="{CAF9D624-66F8-6445-B341-5FB7814EA1EC}"/>
+    <hyperlink ref="D79" r:id="rId5" xr:uid="{8E4D040C-F2AD-264E-BFBB-EC5BA1EB8EA6}"/>
+    <hyperlink ref="D80" r:id="rId6" xr:uid="{685592B0-9268-3D48-8F20-5C3CACABCFD0}"/>
+    <hyperlink ref="D56" r:id="rId7" xr:uid="{8BD21104-6AFB-C946-AA90-6012C50A26B8}"/>
+    <hyperlink ref="D57" r:id="rId8" xr:uid="{2C7A6E24-40B5-2346-9892-F12ACF4DDF91}"/>
+    <hyperlink ref="D28" r:id="rId9" xr:uid="{C3C366B6-6021-0245-BEDE-4316A28D84CC}"/>
+    <hyperlink ref="D76" r:id="rId10" xr:uid="{B8AF1858-6D7F-DF4D-B017-602EA3A527DC}"/>
+    <hyperlink ref="D38" r:id="rId11" xr:uid="{FA050B20-899B-0346-BF0B-7A0573B5A76E}"/>
+    <hyperlink ref="D55" r:id="rId12" xr:uid="{9ED1B634-F68E-AA42-8024-AE9A0D9B46E1}"/>
+    <hyperlink ref="D39" r:id="rId13" xr:uid="{F42864CB-F575-E448-B915-1AC2087A2342}"/>
+    <hyperlink ref="D53" r:id="rId14" xr:uid="{C36FA0DF-7D2A-5543-906C-CF33F5486CDA}"/>
+    <hyperlink ref="D52" r:id="rId15" display="mattbeck@sfsu.edu" xr:uid="{23895FDB-686B-5743-8D35-AE8A257AB947}"/>
+    <hyperlink ref="D63" r:id="rId16" display="melo@mat.uniroma3.it" xr:uid="{37BC4573-0DE8-6746-BC96-48AB40C008BD}"/>
+    <hyperlink ref="D62" r:id="rId17" display="cberkesc@umn.edu" xr:uid="{BE236C2E-741C-3E42-8FC5-E748BC7D909A}"/>
+    <hyperlink ref="D61" r:id="rId18" display="m.hering@ed.ac.uk" xr:uid="{5EAA74B8-78DD-F642-9AA9-B039710F4449}"/>
+    <hyperlink ref="D73" r:id="rId19" display="rossd@sfsu.edu" xr:uid="{2A007655-D6E2-DD46-9C17-49373C01985F}"/>
+    <hyperlink ref="D72" r:id="rId20" display="cberkesc@umn.edu" xr:uid="{62933706-E3A4-B24F-A479-31F0056BB02B}"/>
+    <hyperlink ref="D69" r:id="rId21" display="raluca_vlad@brown.edu" xr:uid="{E35BB1E2-489A-F34B-9A32-B63F808A871C}"/>
+    <hyperlink ref="D71" r:id="rId22" display="mattbeck@sfsu.edu" xr:uid="{87594D2E-82E7-6142-94FA-E485D206F89C}"/>
+    <hyperlink ref="D70" r:id="rId23" display="cberkesc@umn.edu" xr:uid="{F59FB0A7-6722-D34B-B0E2-B75303EE97FD}"/>
+    <hyperlink ref="D75" r:id="rId24" xr:uid="{D8F29A37-7850-FE40-BA66-EFF46D00B7F8}"/>
+    <hyperlink ref="D83" r:id="rId25" xr:uid="{399879DD-3349-5045-910A-E5AC61BF5A76}"/>
+    <hyperlink ref="D84" r:id="rId26" display="mattbeck@sfsu.edu" xr:uid="{18990412-FA5B-BE45-B66D-8EA632253EF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" fitToHeight="0" orientation="portrait" r:id="rId33"/>
+  <pageSetup scale="99" fitToHeight="0" orientation="portrait" r:id="rId27"/>
   <tableParts count="5">
-    <tablePart r:id="rId34"/>
-    <tablePart r:id="rId35"/>
-    <tablePart r:id="rId36"/>
-    <tablePart r:id="rId37"/>
-    <tablePart r:id="rId38"/>
+    <tablePart r:id="rId28"/>
+    <tablePart r:id="rId29"/>
+    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId31"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
